--- a/src/xlsx/outdoor.xlsx
+++ b/src/xlsx/outdoor.xlsx
@@ -1733,6 +1733,7 @@
       </c>
       <c r="K40" s="1" t="n"/>
     </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
@@ -2035,6 +2036,7 @@
       </c>
       <c r="K50" s="1" t="n"/>
     </row>
+    <row r="51"/>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
@@ -5483,6 +5485,7 @@
       </c>
       <c r="K84" s="1" t="n"/>
     </row>
+    <row r="85"/>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
@@ -5728,6 +5731,7 @@
       <c r="J92" s="1" t="n"/>
       <c r="K92" s="1" t="n"/>
     </row>
+    <row r="93"/>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
@@ -6298,6 +6302,7 @@
       </c>
       <c r="K111" s="1" t="n"/>
     </row>
+    <row r="112"/>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
@@ -7140,6 +7145,7 @@
         </is>
       </c>
     </row>
+    <row r="136"/>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
@@ -9158,6 +9164,7 @@
         </is>
       </c>
     </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
@@ -9419,6 +9426,7 @@
       <c r="J56" s="1" t="n"/>
       <c r="K56" s="1" t="n"/>
     </row>
+    <row r="57"/>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
@@ -10125,6 +10133,7 @@
       </c>
       <c r="K81" s="1" t="n"/>
     </row>
+    <row r="82"/>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
@@ -10942,6 +10951,7 @@
       <c r="J104" s="1" t="n"/>
       <c r="K104" s="1" t="n"/>
     </row>
+    <row r="105"/>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
@@ -11723,6 +11733,7 @@
       </c>
       <c r="O126" s="1" t="n"/>
     </row>
+    <row r="127"/>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
@@ -12245,6 +12256,7 @@
         </is>
       </c>
     </row>
+    <row r="145"/>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
@@ -12494,6 +12506,7 @@
         </is>
       </c>
     </row>
+    <row r="155"/>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
@@ -13060,6 +13073,7 @@
         </is>
       </c>
     </row>
+    <row r="173"/>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
@@ -14318,6 +14332,7 @@
       </c>
       <c r="K10" s="1" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -14740,6 +14755,7 @@
       </c>
       <c r="K22" s="1" t="n"/>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
@@ -17585,6 +17601,7 @@
       </c>
       <c r="K112" s="1" t="n"/>
     </row>
+    <row r="113"/>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
@@ -18457,6 +18474,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
@@ -19959,6 +19977,7 @@
         </is>
       </c>
     </row>
+    <row r="61"/>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
@@ -20952,6 +20971,7 @@
       </c>
       <c r="K90" s="1" t="n"/>
     </row>
+    <row r="91"/>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
@@ -21828,6 +21848,7 @@
       </c>
       <c r="K117" s="1" t="n"/>
     </row>
+    <row r="118"/>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
@@ -22484,6 +22505,7 @@
       </c>
       <c r="G138" s="1" t="n"/>
     </row>
+    <row r="139"/>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
@@ -23331,6 +23353,7 @@
         </is>
       </c>
     </row>
+    <row r="165"/>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
@@ -23849,6 +23872,7 @@
         </is>
       </c>
     </row>
+    <row r="185"/>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
@@ -24592,6 +24616,7 @@
       </c>
       <c r="K205" s="1" t="n"/>
     </row>
+    <row r="206"/>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
@@ -25085,6 +25110,7 @@
       </c>
       <c r="K221" s="1" t="n"/>
     </row>
+    <row r="222"/>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
@@ -26234,6 +26260,7 @@
       <c r="J19" s="1" t="n"/>
       <c r="K19" s="1" t="n"/>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
@@ -26596,6 +26623,7 @@
       <c r="J29" s="1" t="n"/>
       <c r="K29" s="1" t="n"/>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
@@ -26933,6 +26961,7 @@
       </c>
       <c r="K39" s="1" t="n"/>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
@@ -27371,6 +27400,7 @@
         </is>
       </c>
     </row>
+    <row r="55"/>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
@@ -28591,6 +28621,7 @@
       <c r="K23" s="1" t="n"/>
       <c r="O23" s="1" t="n"/>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
@@ -28940,6 +28971,7 @@
       <c r="J36" s="1" t="n"/>
       <c r="K36" s="1" t="n"/>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
@@ -29185,6 +29217,7 @@
       <c r="J44" s="1" t="n"/>
       <c r="K44" s="1" t="n"/>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
@@ -29573,6 +29606,7 @@
         </is>
       </c>
     </row>
+    <row r="56"/>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
@@ -30727,6 +30761,7 @@
       </c>
       <c r="K89" s="1" t="n"/>
     </row>
+    <row r="90"/>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
@@ -30993,6 +31028,7 @@
       </c>
       <c r="G100" s="1" t="n"/>
     </row>
+    <row r="101"/>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
@@ -31266,6 +31302,7 @@
         </is>
       </c>
     </row>
+    <row r="113"/>
     <row r="114">
       <c r="B114" t="inlineStr">
         <is>
@@ -31312,6 +31349,7 @@
         </is>
       </c>
     </row>
+    <row r="117"/>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
@@ -31644,6 +31682,7 @@
       </c>
       <c r="G131" s="1" t="n"/>
     </row>
+    <row r="132"/>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
@@ -32788,6 +32827,7 @@
       </c>
       <c r="K166" s="1" t="n"/>
     </row>
+    <row r="167"/>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
@@ -33054,6 +33094,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
@@ -34513,6 +34554,7 @@
       </c>
       <c r="G48" s="1" t="n"/>
     </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
@@ -35323,6 +35365,7 @@
       </c>
       <c r="K73" s="1" t="n"/>
     </row>
+    <row r="74"/>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
@@ -36241,6 +36284,7 @@
         </is>
       </c>
     </row>
+    <row r="104"/>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
@@ -37045,6 +37089,7 @@
         </is>
       </c>
     </row>
+    <row r="128"/>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
@@ -37377,6 +37422,7 @@
         </is>
       </c>
     </row>
+    <row r="140"/>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
@@ -38515,6 +38561,7 @@
       </c>
       <c r="K17" s="1" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
@@ -39264,6 +39311,7 @@
         </is>
       </c>
     </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
@@ -40168,6 +40216,7 @@
         </is>
       </c>
     </row>
+    <row r="78"/>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
@@ -41171,6 +41220,7 @@
       <c r="J107" s="1" t="n"/>
       <c r="K107" s="1" t="n"/>
     </row>
+    <row r="108"/>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
@@ -41379,6 +41429,7 @@
       <c r="J114" s="1" t="n"/>
       <c r="K114" s="1" t="n"/>
     </row>
+    <row r="115"/>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
@@ -41639,6 +41690,7 @@
         </is>
       </c>
     </row>
+    <row r="123"/>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
@@ -41899,6 +41951,7 @@
         </is>
       </c>
     </row>
+    <row r="131"/>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
@@ -42725,6 +42778,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>

--- a/src/xlsx/outdoor.xlsx
+++ b/src/xlsx/outdoor.xlsx
@@ -11960,7 +11960,7 @@
       </c>
       <c r="G135" s="1" t="inlineStr">
         <is>
-          <t>行李滿了。</t>
+          <t>背包滿了。</t>
         </is>
       </c>
       <c r="I135" s="1" t="inlineStr">
@@ -17911,7 +17911,7 @@
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>&lt;RIVAL&gt;：喲！</t>
+          <t>&lt;RIVAL&gt;：嘿！</t>
         </is>
       </c>
       <c r="I3" s="1" t="inlineStr">
@@ -18015,7 +18015,7 @@
       </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
-          <t>你在這兒轉來轉去的，</t>
+          <t>你在這裡轉來轉去的，</t>
         </is>
       </c>
       <c r="I5" s="1" t="inlineStr">
@@ -20122,7 +20122,7 @@
       </c>
       <c r="G65" s="1" t="inlineStr">
         <is>
-          <t>……啥？我嗎？</t>
+          <t>……什麼？我嗎？</t>
         </is>
       </c>
       <c r="I65" s="1" t="inlineStr">
@@ -20764,7 +20764,7 @@
       </c>
       <c r="G85" s="1" t="inlineStr">
         <is>
-          <t>行李已滿了！</t>
+          <t>背包已滿了！</t>
         </is>
       </c>
       <c r="I85" s="1" t="inlineStr">
@@ -21993,7 +21993,7 @@
       </c>
       <c r="G122" s="1" t="inlineStr">
         <is>
-          <t>聽上去還挺有趣的！</t>
+          <t>聽起來還滿有趣的！</t>
         </is>
       </c>
       <c r="I122" s="1" t="inlineStr">
@@ -22835,7 +22835,7 @@
       </c>
       <c r="G149" s="1" t="inlineStr">
         <is>
-          <t>給你跪了……又失敗！</t>
+          <t>唉……又失敗了！</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -28529,7 +28529,7 @@
       </c>
       <c r="G21" s="1" t="inlineStr">
         <is>
-          <t>就是明年的這個時候嘍……</t>
+          <t>大概就是明年這個時候了…</t>
         </is>
       </c>
       <c r="I21" s="1" t="inlineStr">
@@ -32455,7 +32455,7 @@
       </c>
       <c r="G155" s="1" t="inlineStr">
         <is>
-          <t>寶可夢發燒友俱樂部。</t>
+          <t>寶可夢同好會。</t>
         </is>
       </c>
       <c r="I155" s="1" t="inlineStr">
@@ -33575,7 +33575,7 @@
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
-          <t>但是遊戲城令人頭疼！</t>
+          <t>但是遊戲城很傷腦筋！</t>
         </is>
       </c>
       <c r="I20" s="1" t="inlineStr">
@@ -34030,7 +34030,7 @@
       </c>
       <c r="G33" s="1" t="inlineStr">
         <is>
-          <t>哎喲喲！</t>
+          <t>嗨呀！</t>
         </is>
       </c>
       <c r="I33" s="1" t="inlineStr">
@@ -34964,7 +34964,7 @@
       </c>
       <c r="G62" s="1" t="inlineStr">
         <is>
-          <t>行李已滿了。</t>
+          <t>背包已滿了。</t>
         </is>
       </c>
       <c r="I62" s="1" t="inlineStr">
